--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.43942</v>
+        <v>16.65238</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1538</v>
+        <v>16.47285</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2948</v>
+        <v>16.54834</v>
       </c>
       <c r="F2" t="n">
-        <v>21.6109</v>
+        <v>42.5448</v>
       </c>
       <c r="G2" t="n">
-        <v>22.28768</v>
+        <v>0.04994</v>
       </c>
       <c r="H2" t="n">
-        <v>34.49564</v>
+        <v>1.81883</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.62441</v>
+        <v>16.78792</v>
       </c>
       <c r="D3" t="n">
-        <v>15.78475</v>
+        <v>16.40806</v>
       </c>
       <c r="E3" t="n">
-        <v>16.10358</v>
+        <v>16.6702</v>
       </c>
       <c r="F3" t="n">
-        <v>21.45367</v>
+        <v>43.01769</v>
       </c>
       <c r="G3" t="n">
-        <v>21.75244</v>
+        <v>0.05097</v>
       </c>
       <c r="H3" t="n">
-        <v>34.43969</v>
+        <v>1.81711</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67455</v>
+        <v>16.83139</v>
       </c>
       <c r="D4" t="n">
-        <v>15.70654</v>
+        <v>16.42224</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13803</v>
+        <v>16.63193</v>
       </c>
       <c r="F4" t="n">
-        <v>21.59286</v>
+        <v>42.74046</v>
       </c>
       <c r="G4" t="n">
-        <v>22.09882</v>
+        <v>0.05061</v>
       </c>
       <c r="H4" t="n">
-        <v>33.946</v>
+        <v>1.79078</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.67337</v>
+        <v>16.66428</v>
       </c>
       <c r="D5" t="n">
-        <v>15.92965</v>
+        <v>16.17022</v>
       </c>
       <c r="E5" t="n">
-        <v>16.00697</v>
+        <v>16.64608</v>
       </c>
       <c r="F5" t="n">
-        <v>21.37988</v>
+        <v>41.98932</v>
       </c>
       <c r="G5" t="n">
-        <v>22.20383</v>
+        <v>0.05051</v>
       </c>
       <c r="H5" t="n">
-        <v>33.61092</v>
+        <v>1.8216</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61915</v>
+        <v>16.70594</v>
       </c>
       <c r="D6" t="n">
-        <v>15.81584</v>
+        <v>16.56566</v>
       </c>
       <c r="E6" t="n">
-        <v>16.09761</v>
+        <v>16.62722</v>
       </c>
       <c r="F6" t="n">
-        <v>22.17531</v>
+        <v>42.48647</v>
       </c>
       <c r="G6" t="n">
-        <v>21.6234</v>
+        <v>0.05031</v>
       </c>
       <c r="H6" t="n">
-        <v>34.06111</v>
+        <v>1.81057</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67958</v>
+        <v>16.81578</v>
       </c>
       <c r="D7" t="n">
-        <v>16.04816</v>
+        <v>16.65655</v>
       </c>
       <c r="E7" t="n">
-        <v>16.31584</v>
+        <v>16.65999</v>
       </c>
       <c r="F7" t="n">
-        <v>21.74399</v>
+        <v>43.03021</v>
       </c>
       <c r="G7" t="n">
-        <v>21.69887</v>
+        <v>0.05076</v>
       </c>
       <c r="H7" t="n">
-        <v>34.61006</v>
+        <v>1.80535</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.53778</v>
+        <v>16.76265</v>
       </c>
       <c r="D8" t="n">
-        <v>16.02213</v>
+        <v>16.35252</v>
       </c>
       <c r="E8" t="n">
-        <v>16.24263</v>
+        <v>16.55298</v>
       </c>
       <c r="F8" t="n">
-        <v>21.54574</v>
+        <v>42.05989</v>
       </c>
       <c r="G8" t="n">
-        <v>21.64246</v>
+        <v>0.0497</v>
       </c>
       <c r="H8" t="n">
-        <v>33.93941</v>
+        <v>1.77457</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.60644</v>
+        <v>16.88523</v>
       </c>
       <c r="D9" t="n">
-        <v>15.65352</v>
+        <v>16.58761</v>
       </c>
       <c r="E9" t="n">
-        <v>15.99586</v>
+        <v>16.60439</v>
       </c>
       <c r="F9" t="n">
-        <v>21.684</v>
+        <v>42.07954</v>
       </c>
       <c r="G9" t="n">
-        <v>21.66538</v>
+        <v>0.04979</v>
       </c>
       <c r="H9" t="n">
-        <v>33.409</v>
+        <v>1.83981</v>
       </c>
     </row>
     <row r="10">
@@ -660,63 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.72789</v>
+        <v>16.77014</v>
       </c>
       <c r="D10" t="n">
-        <v>15.97865</v>
+        <v>16.50631</v>
       </c>
       <c r="E10" t="n">
-        <v>16.08951</v>
+        <v>16.5743</v>
       </c>
       <c r="F10" t="n">
-        <v>21.16723</v>
+        <v>42.59554</v>
       </c>
       <c r="G10" t="n">
-        <v>21.50207</v>
+        <v>0.05048</v>
       </c>
       <c r="H10" t="n">
-        <v>33.67117</v>
+        <v>1.80475</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -728,32 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.75702</v>
+        <v>16.69284</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0796</v>
+        <v>16.56614</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6071800000000001</v>
+        <v>16.5677</v>
       </c>
       <c r="F12" t="n">
-        <v>0.95875</v>
+        <v>42.47292</v>
       </c>
       <c r="G12" t="n">
-        <v>0.10856</v>
+        <v>0.05058</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.09238</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.12367</v>
+        <v>1.80259</v>
       </c>
     </row>
     <row r="13">
@@ -763,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7500599999999999</v>
+        <v>17.00673</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08187</v>
+        <v>16.42358</v>
       </c>
       <c r="E13" t="n">
-        <v>0.59268</v>
+        <v>16.6006</v>
       </c>
       <c r="F13" t="n">
-        <v>0.97602</v>
+        <v>41.84579</v>
       </c>
       <c r="G13" t="n">
-        <v>0.10711</v>
+        <v>0.05112</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09263</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.12565</v>
+        <v>1.81053</v>
       </c>
     </row>
     <row r="14">
@@ -794,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.75262</v>
+        <v>16.92212</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08223</v>
+        <v>16.68563</v>
       </c>
       <c r="E14" t="n">
-        <v>0.60583</v>
+        <v>16.83959</v>
       </c>
       <c r="F14" t="n">
-        <v>0.95524</v>
+        <v>42.31667</v>
       </c>
       <c r="G14" t="n">
-        <v>0.10909</v>
+        <v>0.04995</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09146</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.12579</v>
+        <v>1.78929</v>
       </c>
     </row>
     <row r="15">
@@ -825,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7413999999999999</v>
+        <v>16.81228</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0805</v>
+        <v>16.51574</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5970299999999999</v>
+        <v>16.56423</v>
       </c>
       <c r="F15" t="n">
-        <v>0.96408</v>
+        <v>42.44432</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1093</v>
+        <v>0.0497</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09268999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.12585</v>
+        <v>1.79311</v>
       </c>
     </row>
     <row r="16">
@@ -856,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.74638</v>
+        <v>16.77873</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08076</v>
+        <v>16.57127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6076</v>
+        <v>16.6717</v>
       </c>
       <c r="F16" t="n">
-        <v>0.97575</v>
+        <v>42.4413</v>
       </c>
       <c r="G16" t="n">
-        <v>0.10729</v>
+        <v>0.05041</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09157</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.12441</v>
+        <v>1.77855</v>
       </c>
     </row>
     <row r="17">
@@ -887,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.75168</v>
+        <v>16.85846</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08097</v>
+        <v>16.4077</v>
       </c>
       <c r="E17" t="n">
-        <v>0.60176</v>
+        <v>16.50726</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95002</v>
+        <v>42.3033</v>
       </c>
       <c r="G17" t="n">
-        <v>0.10958</v>
+        <v>0.05005</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09209000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.12556</v>
+        <v>1.78862</v>
       </c>
     </row>
     <row r="18">
@@ -918,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.74469</v>
+        <v>17.1214</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08051999999999999</v>
+        <v>16.41777</v>
       </c>
       <c r="E18" t="n">
-        <v>0.60163</v>
+        <v>16.62747</v>
       </c>
       <c r="F18" t="n">
-        <v>0.97742</v>
+        <v>42.45712</v>
       </c>
       <c r="G18" t="n">
-        <v>0.11147</v>
+        <v>0.05079</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00746</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09157</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12537</v>
+        <v>1.81287</v>
       </c>
     </row>
     <row r="19">
@@ -949,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.76479</v>
+        <v>16.89544</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08097</v>
+        <v>16.47507</v>
       </c>
       <c r="E19" t="n">
-        <v>0.59221</v>
+        <v>16.78839</v>
       </c>
       <c r="F19" t="n">
-        <v>0.92579</v>
+        <v>42.09616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.10733</v>
+        <v>0.0507</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.12723</v>
+        <v>1.80474</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +922,1274 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.75573</v>
+        <v>16.63531</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08086</v>
+        <v>16.43224</v>
       </c>
       <c r="E20" t="n">
-        <v>0.60284</v>
+        <v>16.56806</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9622000000000001</v>
+        <v>42.27093</v>
       </c>
       <c r="G20" t="n">
-        <v>0.10809</v>
+        <v>0.04954</v>
       </c>
       <c r="H20" t="n">
+        <v>1.77732</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.63265</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.27127</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.44661</v>
+      </c>
+      <c r="F22" t="n">
+        <v>254.87228</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.67526</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.21087</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.29497</v>
+      </c>
+      <c r="F23" t="n">
+        <v>250.2602</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.7542</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.37249</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.44092</v>
+      </c>
+      <c r="F24" t="n">
+        <v>254.40972</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.64279</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.41412</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.47975</v>
+      </c>
+      <c r="F25" t="n">
+        <v>252.42801</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.81207</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.33458</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.6094</v>
+      </c>
+      <c r="F26" t="n">
+        <v>248.33182</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.92455</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.27347</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.43695</v>
+      </c>
+      <c r="F27" t="n">
+        <v>253.11244</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.88036</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.58066</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.6627</v>
+      </c>
+      <c r="F28" t="n">
+        <v>253.84273</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.58548</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.53084</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.55582</v>
+      </c>
+      <c r="F29" t="n">
+        <v>249.92969</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.59809</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.42915</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.54702</v>
+      </c>
+      <c r="F30" t="n">
+        <v>250.15412</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.74446</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.99059</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.20493</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.66061</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.03116</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.64233</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.95034</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.4051</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.08273</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.5779</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.70502</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.72575</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.12396</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.8393</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.21081</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.54833</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.80033</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.43738</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.57879</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.83183</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.57342</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.90012</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.30576</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.55835</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.77569</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.03035</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.7233</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.12438</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.56397</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.93208</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.70101</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.59499</v>
+      </c>
+      <c r="E38" t="n">
+        <v>15.78708</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.36585</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.17735</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.8589</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.08136</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.54429</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.73015</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.96016</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.71182</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.81251</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.12916</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.67689</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.55745</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.62064</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.59375</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.59626</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.51385</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.3003</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.69028</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.56365</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.19395</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.41838</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.29439</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.7774</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.79024</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.28688</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.71981</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.64145</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.54933</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.19158</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.20059</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.44094</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.35941</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.46144</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.53973</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.32047</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20.91355</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.78343</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.02753</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.92595</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.57808</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.2553</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.04802</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.55323</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.65432</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.27672</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.79742</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33.72936</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.51523</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.04792</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.45881</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.05216</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.66711</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.44401</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.0351</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.09358</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.74129</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.35029</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.59383</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.11925</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.10742</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60853</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.11898</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.61968</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.11015</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61953</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.10529</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60599</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.10923</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60847</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.0872</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60127</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.11937</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61011</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.12878</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.60116</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.10039</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6043500000000001</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.08668</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.60307</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.09739</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.61298</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.09397</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.59556</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.10831</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61106</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.11413</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61143</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.12992</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60342</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.11891</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.59344</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.1092</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.7415</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.60936</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09198000000000001</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12655</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75871</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.07978</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.60982</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.94386</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09152</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12423</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.74151</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.07988000000000001</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60246</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9524899999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.11021</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.00747</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.09276</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.1278</v>
+      <c r="I74" t="n">
+        <v>0.09134</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12895</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75478</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08066</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60247</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.95587</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10835</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09221</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1247</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75776</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08073</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.61356</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.98989</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12726</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.75078</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60923</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.95707</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10501</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09336999999999999</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12678</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.73743</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08071</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60434</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9579299999999999</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10898</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09159</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12593</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.7468900000000001</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08087999999999999</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6196199999999999</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9537099999999999</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10979</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09224</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12337</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.76039</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08205</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.61067</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9521500000000001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.10698</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09359000000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12457</v>
       </c>
     </row>
   </sheetData>
